--- a/grupos/1FM - Estadisticos 20221.xlsx
+++ b/grupos/1FM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="186">
   <si>
     <t>Materia</t>
   </si>
@@ -179,6 +179,9 @@
     <t>VASQUEZ AVALOS GIOVANNI</t>
   </si>
   <si>
+    <t>VELASCO SAN JUAN DULCE REGINA</t>
+  </si>
+  <si>
     <t>ZAVALA DELGADO AXEL GAEL</t>
   </si>
   <si>
@@ -209,24 +212,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
+    <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -239,54 +242,156 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>IVETTE NAOMI</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
     <t>BAEZ</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>CAMARILLO</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>CALOCA</t>
+  </si>
+  <si>
     <t>CALVO</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
     <t>COCOTLE</t>
   </si>
   <si>
+    <t>CORRO</t>
+  </si>
+  <si>
     <t>COYOHUA</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>LEON</t>
   </si>
   <si>
     <t>LUCIO</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>NATIVIDAD</t>
+  </si>
+  <si>
+    <t>ORTIGOZA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
     <t>ZAVALA</t>
   </si>
   <si>
+    <t>ZAVALETA</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
     <t>MONTIEL</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
     <t>URIAS</t>
   </si>
   <si>
     <t>VERA</t>
   </si>
   <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
@@ -302,36 +407,93 @@
     <t>TEZOCO</t>
   </si>
   <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>GAMBINO</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
     <t>MORENO</t>
   </si>
   <si>
     <t>ARELLANO</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
+    <t>VOTTE</t>
   </si>
   <si>
     <t>ZARATE</t>
   </si>
   <si>
+    <t>ARGUELLES</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
     <t>LUNA</t>
   </si>
   <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>AVALOS</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
     <t>DELGADO</t>
   </si>
   <si>
+    <t>CAMILA JEZABEL</t>
+  </si>
+  <si>
     <t>EDUARDO EMER</t>
   </si>
   <si>
+    <t>ISAAC ASAEL</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>EDNA YOSSELIN</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
     <t>LESLY VIANEY</t>
   </si>
   <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>ERICK ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ARLETH MALERY</t>
+  </si>
+  <si>
     <t>ANGEL EMMANUEL</t>
   </si>
   <si>
     <t>RUFINA ISABEL</t>
   </si>
   <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
     <t>LUIS BRANDON</t>
   </si>
   <si>
@@ -341,229 +503,79 @@
     <t>GLORIA</t>
   </si>
   <si>
+    <t>DINORAH AZUL</t>
+  </si>
+  <si>
     <t>MARIAM</t>
   </si>
   <si>
     <t>MARIO</t>
   </si>
   <si>
+    <t>LLUVIA RUBI</t>
+  </si>
+  <si>
+    <t>MARIA PAULINA</t>
+  </si>
+  <si>
+    <t>WENDY</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
     <t>NILO</t>
   </si>
   <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>IVETTE NAOMI</t>
+    <t>KAY LEILANI</t>
   </si>
   <si>
     <t>OSMAR UZIEL</t>
   </si>
   <si>
+    <t>JEAN KARLLO</t>
+  </si>
+  <si>
+    <t>GEOVANI</t>
+  </si>
+  <si>
+    <t>JULIO</t>
+  </si>
+  <si>
+    <t>KEVIN GAEL</t>
+  </si>
+  <si>
     <t>GUSTAVO</t>
   </si>
   <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>JUAN MANUEL</t>
+  </si>
+  <si>
+    <t>ANGEL GUILLERMO</t>
+  </si>
+  <si>
+    <t>STEPHANIE</t>
+  </si>
+  <si>
+    <t>CALEB ELI</t>
+  </si>
+  <si>
+    <t>GERARDO ALBERTO</t>
+  </si>
+  <si>
+    <t>GIOVANNI</t>
+  </si>
+  <si>
+    <t>FRIDA SOFIA</t>
+  </si>
+  <si>
+    <t>DULCE REGINA</t>
+  </si>
+  <si>
     <t>AXEL GAEL</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>CAMARILLO</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>CALOCA</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>CORRO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>NATIVIDAD</t>
-  </si>
-  <si>
-    <t>ORTIGOZA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>ZAVALETA</t>
-  </si>
-  <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>GAMBINO</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>VOTTE</t>
-  </si>
-  <si>
-    <t>ARGUELLES</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>AVALOS</t>
-  </si>
-  <si>
-    <t>CAMILA JEZABEL</t>
-  </si>
-  <si>
-    <t>ISAAC ASAEL</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>EDNA YOSSELIN</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
-  </si>
-  <si>
-    <t>ERICK ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ARLETH MALERY</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>DINORAH AZUL</t>
-  </si>
-  <si>
-    <t>LLUVIA RUBI</t>
-  </si>
-  <si>
-    <t>MARIA PAULINA</t>
-  </si>
-  <si>
-    <t>WENDY</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>KAY LEILANI</t>
-  </si>
-  <si>
-    <t>JEAN KARLLO</t>
-  </si>
-  <si>
-    <t>GEOVANI</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
-    <t>KEVIN GAEL</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>JUAN MANUEL</t>
-  </si>
-  <si>
-    <t>ANGEL GUILLERMO</t>
-  </si>
-  <si>
-    <t>STEPHANIE</t>
-  </si>
-  <si>
-    <t>CALEB ELI</t>
-  </si>
-  <si>
-    <t>GERARDO ALBERTO</t>
-  </si>
-  <si>
-    <t>GIOVANNI</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
   </si>
 </sst>
 </file>
@@ -921,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y45"/>
+  <dimension ref="A1:Y46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1067,10 +1079,10 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
         <v>-1</v>
@@ -1079,7 +1091,7 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1138,16 +1150,16 @@
         <v>9</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G5">
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -1156,7 +1168,7 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1180,10 +1192,10 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -1192,7 +1204,7 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>9</v>
@@ -1221,10 +1233,10 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -1233,7 +1245,7 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1298,10 +1310,10 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1310,7 +1322,7 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1375,10 +1387,10 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1387,7 +1399,7 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1423,7 +1435,7 @@
         <v>8</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1446,16 +1458,16 @@
         <v>5</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G9">
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -1464,7 +1476,7 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1491,7 +1503,7 @@
         <v>6</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>5</v>
@@ -1500,7 +1512,7 @@
         <v>5</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y9">
         <v>5</v>
@@ -1529,10 +1541,10 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
         <v>-1</v>
@@ -1541,7 +1553,7 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1565,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>10</v>
@@ -1606,10 +1618,10 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
         <v>-1</v>
@@ -1618,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1654,7 +1666,7 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1683,10 +1695,10 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1695,7 +1707,7 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1754,16 +1766,16 @@
         <v>6</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G13">
         <v>7</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1772,7 +1784,7 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1799,7 +1811,7 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>6</v>
@@ -1808,7 +1820,7 @@
         <v>6</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -1831,16 +1843,16 @@
         <v>7</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G14">
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
         <v>-1</v>
@@ -1849,7 +1861,7 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1873,7 +1885,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>10</v>
@@ -1885,7 +1897,7 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1914,10 +1926,10 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>-1</v>
@@ -1926,7 +1938,7 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1991,10 +2003,10 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
         <v>-1</v>
@@ -2003,7 +2015,7 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -2027,7 +2039,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>10</v>
@@ -2062,16 +2074,16 @@
         <v>8</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G17">
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
         <v>-1</v>
@@ -2080,7 +2092,7 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2104,7 +2116,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>10</v>
@@ -2116,7 +2128,7 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>9</v>
@@ -2139,16 +2151,16 @@
         <v>6</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G18">
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
         <v>-1</v>
@@ -2157,7 +2169,7 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2193,7 +2205,7 @@
         <v>6</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2216,16 +2228,16 @@
         <v>6</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G19">
         <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -2234,7 +2246,7 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2261,7 +2273,7 @@
         <v>6</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>7</v>
@@ -2270,7 +2282,7 @@
         <v>6</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -2293,16 +2305,16 @@
         <v>5</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G20">
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>-1</v>
@@ -2311,7 +2323,7 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2338,7 +2350,7 @@
         <v>6</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>5</v>
@@ -2347,7 +2359,7 @@
         <v>5</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2376,10 +2388,10 @@
         <v>8</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>-1</v>
@@ -2388,7 +2400,7 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2441,22 +2453,22 @@
         <v>5</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>5</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G22">
         <v>5</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>-1</v>
@@ -2465,7 +2477,7 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2492,16 +2504,16 @@
         <v>6</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>5</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2530,10 +2542,10 @@
         <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -2542,7 +2554,7 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2566,10 +2578,10 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>9</v>
@@ -2607,10 +2619,10 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
         <v>-1</v>
@@ -2619,7 +2631,7 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2684,10 +2696,10 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
         <v>-1</v>
@@ -2696,7 +2708,7 @@
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2720,7 +2732,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>10</v>
@@ -2761,10 +2773,10 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
         <v>-1</v>
@@ -2773,7 +2785,7 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2809,7 +2821,7 @@
         <v>8</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -2832,16 +2844,16 @@
         <v>5</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G27">
         <v>5</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>-1</v>
@@ -2850,7 +2862,7 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2877,7 +2889,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>5</v>
@@ -2886,7 +2898,7 @@
         <v>5</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y27">
         <v>5</v>
@@ -2909,16 +2921,16 @@
         <v>5</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G28">
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
         <v>-1</v>
@@ -2927,7 +2939,7 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2963,7 +2975,7 @@
         <v>5</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y28">
         <v>5</v>
@@ -2992,10 +3004,10 @@
         <v>-1</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
         <v>-1</v>
@@ -3004,7 +3016,7 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -3028,10 +3040,10 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -3069,10 +3081,10 @@
         <v>6</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
         <v>-1</v>
@@ -3081,7 +3093,7 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -3134,22 +3146,22 @@
         <v>8</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E31">
         <v>7</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G31">
         <v>5</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
         <v>-1</v>
@@ -3158,7 +3170,7 @@
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3182,19 +3194,19 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W31">
         <v>7</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y31">
         <v>5</v>
@@ -3223,10 +3235,10 @@
         <v>7</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
         <v>-1</v>
@@ -3235,7 +3247,7 @@
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3271,7 +3283,7 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>7</v>
@@ -3300,10 +3312,10 @@
         <v>9</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
         <v>-1</v>
@@ -3312,7 +3324,7 @@
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3348,7 +3360,7 @@
         <v>8</v>
       </c>
       <c r="X33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y33">
         <v>9</v>
@@ -3377,10 +3389,10 @@
         <v>8</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
         <v>-1</v>
@@ -3389,7 +3401,7 @@
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3448,16 +3460,16 @@
         <v>6</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G35">
         <v>5</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J35">
         <v>-1</v>
@@ -3466,7 +3478,7 @@
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3490,7 +3502,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U35">
         <v>9</v>
@@ -3502,7 +3514,7 @@
         <v>6</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y35">
         <v>5</v>
@@ -3531,10 +3543,10 @@
         <v>8</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J36">
         <v>-1</v>
@@ -3543,7 +3555,7 @@
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -3567,7 +3579,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U36">
         <v>9</v>
@@ -3608,10 +3620,10 @@
         <v>8</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
         <v>-1</v>
@@ -3620,7 +3632,7 @@
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M37">
         <v>-1</v>
@@ -3685,10 +3697,10 @@
         <v>7</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J38">
         <v>-1</v>
@@ -3697,7 +3709,7 @@
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M38">
         <v>-1</v>
@@ -3721,7 +3733,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U38">
         <v>10</v>
@@ -3762,10 +3774,10 @@
         <v>6</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J39">
         <v>-1</v>
@@ -3774,7 +3786,7 @@
         <v>-1</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M39">
         <v>-1</v>
@@ -3810,7 +3822,7 @@
         <v>6</v>
       </c>
       <c r="X39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y39">
         <v>6</v>
@@ -3839,10 +3851,10 @@
         <v>8</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J40">
         <v>-1</v>
@@ -3851,7 +3863,7 @@
         <v>-1</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M40">
         <v>-1</v>
@@ -3878,7 +3890,7 @@
         <v>7</v>
       </c>
       <c r="U40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V40">
         <v>7</v>
@@ -3916,10 +3928,10 @@
         <v>8</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J41">
         <v>-1</v>
@@ -3928,7 +3940,7 @@
         <v>-1</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M41">
         <v>-1</v>
@@ -3993,10 +4005,10 @@
         <v>7</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J42">
         <v>-1</v>
@@ -4005,7 +4017,7 @@
         <v>-1</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M42">
         <v>-1</v>
@@ -4029,10 +4041,10 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V42">
         <v>8</v>
@@ -4070,10 +4082,10 @@
         <v>8</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J43">
         <v>-1</v>
@@ -4082,7 +4094,7 @@
         <v>-1</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M43">
         <v>-1</v>
@@ -4147,10 +4159,10 @@
         <v>9</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J44">
         <v>-1</v>
@@ -4159,7 +4171,7 @@
         <v>-1</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M44">
         <v>-1</v>
@@ -4183,7 +4195,7 @@
         <v>-1</v>
       </c>
       <c r="T44">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U44">
         <v>10</v>
@@ -4195,7 +4207,7 @@
         <v>8</v>
       </c>
       <c r="X44">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y44">
         <v>9</v>
@@ -4206,28 +4218,28 @@
         <v>53</v>
       </c>
       <c r="B45">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C45">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E45">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G45">
         <v>6</v>
       </c>
       <c r="H45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J45">
         <v>-1</v>
@@ -4236,7 +4248,7 @@
         <v>-1</v>
       </c>
       <c r="L45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M45">
         <v>-1</v>
@@ -4260,21 +4272,98 @@
         <v>-1</v>
       </c>
       <c r="T45">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U45">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W45">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25">
+      <c r="A46" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46">
+        <v>9</v>
+      </c>
+      <c r="C46">
+        <v>10</v>
+      </c>
+      <c r="D46">
+        <v>7</v>
+      </c>
+      <c r="E46">
+        <v>6</v>
+      </c>
+      <c r="F46">
+        <v>6</v>
+      </c>
+      <c r="G46">
+        <v>6</v>
+      </c>
+      <c r="H46">
+        <v>6</v>
+      </c>
+      <c r="I46">
+        <v>6</v>
+      </c>
+      <c r="J46">
+        <v>-1</v>
+      </c>
+      <c r="K46">
+        <v>-1</v>
+      </c>
+      <c r="L46">
+        <v>5</v>
+      </c>
+      <c r="M46">
+        <v>-1</v>
+      </c>
+      <c r="N46">
+        <v>-1</v>
+      </c>
+      <c r="O46">
+        <v>-1</v>
+      </c>
+      <c r="P46">
+        <v>-1</v>
+      </c>
+      <c r="Q46">
+        <v>-1</v>
+      </c>
+      <c r="R46">
+        <v>-1</v>
+      </c>
+      <c r="S46">
+        <v>-1</v>
+      </c>
+      <c r="T46">
+        <v>8</v>
+      </c>
+      <c r="U46">
+        <v>8</v>
+      </c>
+      <c r="V46">
+        <v>7</v>
+      </c>
+      <c r="W46">
+        <v>6</v>
+      </c>
+      <c r="X46">
+        <v>5</v>
+      </c>
+      <c r="Y46">
         <v>6</v>
       </c>
     </row>
@@ -4302,153 +4391,153 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>66.67</v>
+        <v>74.42</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>23.26</v>
       </c>
       <c r="H2">
         <v>7.2</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>33.33</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>73.81</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G3">
-        <v>23.81</v>
+        <v>18.6</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>2.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>80.95</v>
+        <v>83.72</v>
       </c>
       <c r="G4">
-        <v>14.29</v>
+        <v>16.28</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>83.33</v>
+        <v>86.05</v>
       </c>
       <c r="G5">
-        <v>16.67</v>
+        <v>13.95</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4459,28 +4548,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6">
+        <v>43</v>
+      </c>
+      <c r="D6">
         <v>42</v>
       </c>
-      <c r="D6">
-        <v>39</v>
-      </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>92.86</v>
+        <v>97.67</v>
       </c>
       <c r="G6">
-        <v>7.14</v>
+        <v>2.33</v>
       </c>
       <c r="H6">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4491,28 +4580,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7">
+        <v>43</v>
+      </c>
+      <c r="D7">
         <v>42</v>
-      </c>
-      <c r="D7">
-        <v>41</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>97.62</v>
+        <v>97.67</v>
       </c>
       <c r="G7">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4528,7 +4617,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4537,16 +4626,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -4557,342 +4646,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>22330051920150</v>
+        <v>22330051920269</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920155</v>
-      </c>
-      <c r="B3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920152</v>
-      </c>
-      <c r="B4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920384</v>
-      </c>
-      <c r="B5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920161</v>
-      </c>
-      <c r="B6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920158</v>
-      </c>
-      <c r="B7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920159</v>
-      </c>
-      <c r="B8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D8" t="s">
-        <v>106</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920160</v>
-      </c>
-      <c r="B9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" t="s">
-        <v>107</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920296</v>
-      </c>
-      <c r="B10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920296</v>
-      </c>
-      <c r="B11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D11" t="s">
-        <v>108</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920267</v>
-      </c>
-      <c r="B12" t="s">
-        <v>80</v>
-      </c>
-      <c r="C12" t="s">
-        <v>94</v>
-      </c>
-      <c r="D12" t="s">
-        <v>109</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920166</v>
-      </c>
-      <c r="B13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13" t="s">
-        <v>110</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920269</v>
-      </c>
-      <c r="B14" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" t="s">
-        <v>111</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920382</v>
-      </c>
-      <c r="B15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" t="s">
-        <v>97</v>
-      </c>
-      <c r="D15" t="s">
-        <v>112</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920382</v>
-      </c>
-      <c r="B16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" t="s">
-        <v>112</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920386</v>
-      </c>
-      <c r="B17" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920176</v>
-      </c>
-      <c r="B18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" t="s">
-        <v>114</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -4902,7 +4671,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4911,53 +4680,53 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920296</v>
+        <v>22330051920269</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920382</v>
+        <v>22330051920149</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4965,234 +4734,234 @@
         <v>22330051920150</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920155</v>
+        <v>22330051920151</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920152</v>
+        <v>22330051920292</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920384</v>
+        <v>22330051920383</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>149</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920161</v>
+        <v>22330051920153</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920158</v>
+        <v>22330051920155</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920159</v>
+        <v>22330051920156</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920160</v>
+        <v>22330051920154</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920267</v>
+        <v>22330051920381</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>154</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920166</v>
+        <v>22330051920152</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920269</v>
+        <v>22330051920384</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920386</v>
+        <v>22330051920157</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920176</v>
+        <v>22330051920161</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920149</v>
+        <v>22330051920158</v>
       </c>
       <c r="B17" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="D17" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -5200,16 +4969,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920151</v>
+        <v>22330051920159</v>
       </c>
       <c r="B18" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="D18" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -5217,16 +4986,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920292</v>
+        <v>22330051920162</v>
       </c>
       <c r="B19" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -5234,16 +5003,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920383</v>
+        <v>22330051920160</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="D20" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5251,16 +5020,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920153</v>
+        <v>22330051920296</v>
       </c>
       <c r="B21" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -5268,16 +5037,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920156</v>
+        <v>22330051920163</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>143</v>
+        <v>94</v>
       </c>
       <c r="D22" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -5285,16 +5054,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920154</v>
+        <v>22330051920165</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D23" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -5302,16 +5071,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920381</v>
+        <v>22330051920385</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="D24" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -5319,16 +5088,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920157</v>
+        <v>22330051920164</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="D25" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -5336,16 +5105,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920162</v>
+        <v>22330051920267</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s">
         <v>132</v>
       </c>
       <c r="D26" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -5353,16 +5122,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920163</v>
+        <v>22330051920166</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D27" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -5370,16 +5139,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920165</v>
+        <v>22330051920167</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D28" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -5387,16 +5156,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920385</v>
+        <v>22330051920382</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="D29" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -5404,16 +5173,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920164</v>
+        <v>22330051920168</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
-        <v>148</v>
+        <v>74</v>
       </c>
       <c r="D30" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -5421,16 +5190,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920167</v>
+        <v>22330051920169</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="D31" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -5438,16 +5207,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>22330051920168</v>
+        <v>22330051920170</v>
       </c>
       <c r="B32" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="D32" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -5455,16 +5224,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>22330051920169</v>
+        <v>22330051920275</v>
       </c>
       <c r="B33" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>150</v>
+        <v>87</v>
       </c>
       <c r="D33" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -5472,16 +5241,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>22330051920170</v>
+        <v>22330051920386</v>
       </c>
       <c r="B34" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="C34" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="D34" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -5489,16 +5258,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>22330051920275</v>
+        <v>22330051920172</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>139</v>
       </c>
       <c r="D35" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -5506,16 +5275,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>22330051920172</v>
+        <v>22330051920278</v>
       </c>
       <c r="B36" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>152</v>
+        <v>94</v>
       </c>
       <c r="D36" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -5523,16 +5292,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>22330051920278</v>
+        <v>22330051920173</v>
       </c>
       <c r="B37" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="D37" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -5540,16 +5309,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>22330051920173</v>
+        <v>22330051920171</v>
       </c>
       <c r="B38" t="s">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="C38" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D38" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -5557,16 +5326,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>22330051920171</v>
+        <v>22330051920174</v>
       </c>
       <c r="B39" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="C39" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="D39" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -5574,16 +5343,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>22330051920174</v>
+        <v>22330051920387</v>
       </c>
       <c r="B40" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="C40" t="s">
-        <v>154</v>
+        <v>94</v>
       </c>
       <c r="D40" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -5591,16 +5360,16 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>22330051920387</v>
+        <v>22330051920284</v>
       </c>
       <c r="B41" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C41" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="D41" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -5608,16 +5377,16 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>22330051920284</v>
+        <v>22330051920175</v>
       </c>
       <c r="B42" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="C42" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="D42" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -5625,18 +5394,35 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43">
-        <v>22330051920175</v>
+        <v>22330051920287</v>
       </c>
       <c r="B43" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="C43" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="D43" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44">
+        <v>22330051920176</v>
+      </c>
+      <c r="B44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44" t="s">
+        <v>144</v>
+      </c>
+      <c r="D44" t="s">
+        <v>185</v>
+      </c>
+      <c r="E44">
         <v>0</v>
       </c>
     </row>
@@ -5647,7 +5433,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5656,22 +5442,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -5679,39 +5465,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920155</v>
+        <v>22330051920160</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920155</v>
+        <v>22330051920160</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5725,39 +5511,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920386</v>
+        <v>22330051920382</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920386</v>
+        <v>22330051920382</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5771,45 +5557,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920150</v>
+        <v>22330051920292</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920292</v>
+        <v>22330051920155</v>
       </c>
       <c r="B7" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="D7" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5817,140 +5603,117 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920384</v>
+        <v>22330051920157</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>157</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920157</v>
+        <v>22330051920269</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>145</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>163</v>
+        <v>76</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920158</v>
+        <v>22330051920386</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>175</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920269</v>
+        <v>22330051920172</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>176</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920172</v>
+        <v>22330051920176</v>
       </c>
       <c r="B12" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="C12" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D12" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G12">
         <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920176</v>
-      </c>
-      <c r="B13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" t="s">
-        <v>99</v>
-      </c>
-      <c r="D13" t="s">
-        <v>114</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/1FM - Estadisticos 20221.xlsx
+++ b/grupos/1FM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="186">
   <si>
     <t>Materia</t>
   </si>
@@ -215,10 +215,10 @@
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>Herrera Serrano Mayra Iliana</t>
@@ -1085,16 +1085,16 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1124,7 +1124,7 @@
         <v>9</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1162,16 +1162,16 @@
         <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1201,13 +1201,13 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1239,16 +1239,16 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1275,7 +1275,7 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>8</v>
@@ -1316,16 +1316,16 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1355,7 +1355,7 @@
         <v>8</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -1393,16 +1393,16 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1432,13 +1432,13 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1470,16 +1470,16 @@
         <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1547,16 +1547,16 @@
         <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1586,13 +1586,13 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1624,16 +1624,16 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
         <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1663,7 +1663,7 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
         <v>9</v>
@@ -1701,16 +1701,16 @@
         <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1737,7 +1737,7 @@
         <v>10</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1746,7 +1746,7 @@
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1778,16 +1778,16 @@
         <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1814,7 +1814,7 @@
         <v>9</v>
       </c>
       <c r="V13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -1823,7 +1823,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1855,16 +1855,16 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1894,13 +1894,13 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1932,16 +1932,16 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1968,10 +1968,10 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -2009,16 +2009,16 @@
         <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2045,7 +2045,7 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>5</v>
@@ -2054,7 +2054,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2086,16 +2086,16 @@
         <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2122,7 +2122,7 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2131,7 +2131,7 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2163,16 +2163,16 @@
         <v>7</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2202,7 +2202,7 @@
         <v>5</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X18">
         <v>5</v>
@@ -2240,16 +2240,16 @@
         <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2276,10 +2276,10 @@
         <v>7</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>5</v>
@@ -2317,16 +2317,16 @@
         <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2394,16 +2394,16 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2433,7 +2433,7 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2471,16 +2471,16 @@
         <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2548,16 +2548,16 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
         <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2584,16 +2584,16 @@
         <v>9</v>
       </c>
       <c r="V23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2625,16 +2625,16 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
         <v>7</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2661,16 +2661,16 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2702,16 +2702,16 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>7</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2741,13 +2741,13 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>8</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2779,16 +2779,16 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
         <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2818,7 +2818,7 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>7</v>
@@ -2856,16 +2856,16 @@
         <v>5</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>6</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2933,16 +2933,16 @@
         <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>5</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -3010,10 +3010,10 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>6</v>
@@ -3049,7 +3049,7 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -3087,16 +3087,16 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
         <v>7</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3132,7 +3132,7 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3164,16 +3164,16 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
         <v>6</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3241,16 +3241,16 @@
         <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
         <v>8</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3280,13 +3280,13 @@
         <v>9</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3318,16 +3318,16 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
         <v>8</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3357,13 +3357,13 @@
         <v>9</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3395,16 +3395,16 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
         <v>8</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3431,10 +3431,10 @@
         <v>10</v>
       </c>
       <c r="V34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X34">
         <v>8</v>
@@ -3472,16 +3472,16 @@
         <v>8</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L35">
         <v>6</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3508,10 +3508,10 @@
         <v>9</v>
       </c>
       <c r="V35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X35">
         <v>6</v>
@@ -3549,16 +3549,16 @@
         <v>9</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L36">
         <v>6</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3585,16 +3585,16 @@
         <v>9</v>
       </c>
       <c r="V36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X36">
         <v>6</v>
       </c>
       <c r="Y36">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3626,16 +3626,16 @@
         <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L37">
         <v>7</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3665,7 +3665,7 @@
         <v>9</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>7</v>
@@ -3703,16 +3703,16 @@
         <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L38">
         <v>7</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3742,7 +3742,7 @@
         <v>9</v>
       </c>
       <c r="W38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X38">
         <v>7</v>
@@ -3783,13 +3783,13 @@
         <v>-1</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L39">
         <v>8</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3819,7 +3819,7 @@
         <v>5</v>
       </c>
       <c r="W39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X39">
         <v>7</v>
@@ -3857,16 +3857,16 @@
         <v>10</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L40">
         <v>7</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3896,13 +3896,13 @@
         <v>7</v>
       </c>
       <c r="W40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>7</v>
       </c>
       <c r="Y40">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3934,16 +3934,16 @@
         <v>10</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L41">
         <v>8</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3973,13 +3973,13 @@
         <v>10</v>
       </c>
       <c r="W41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X41">
         <v>9</v>
       </c>
       <c r="Y41">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -4011,16 +4011,16 @@
         <v>8</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L42">
         <v>8</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -4047,10 +4047,10 @@
         <v>9</v>
       </c>
       <c r="V42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W42">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X42">
         <v>8</v>
@@ -4088,16 +4088,16 @@
         <v>10</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L43">
         <v>6</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -4127,7 +4127,7 @@
         <v>8</v>
       </c>
       <c r="W43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X43">
         <v>6</v>
@@ -4165,16 +4165,16 @@
         <v>10</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L44">
         <v>8</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N44">
         <v>-1</v>
@@ -4204,7 +4204,7 @@
         <v>9</v>
       </c>
       <c r="W44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X44">
         <v>8</v>
@@ -4242,16 +4242,16 @@
         <v>8</v>
       </c>
       <c r="J45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L45">
         <v>6</v>
       </c>
       <c r="M45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N45">
         <v>-1</v>
@@ -4278,10 +4278,10 @@
         <v>7</v>
       </c>
       <c r="V45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W45">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X45">
         <v>7</v>
@@ -4319,16 +4319,16 @@
         <v>6</v>
       </c>
       <c r="J46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L46">
         <v>5</v>
       </c>
       <c r="M46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N46">
         <v>-1</v>
@@ -4355,16 +4355,16 @@
         <v>8</v>
       </c>
       <c r="V46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W46">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X46">
         <v>5</v>
       </c>
       <c r="Y46">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4441,7 +4441,7 @@
         <v>23.26</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -4452,7 +4452,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -4461,19 +4461,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>81.40000000000001</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="G3">
-        <v>18.6</v>
+        <v>20.93</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -4493,19 +4493,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>83.72</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="G4">
-        <v>16.28</v>
+        <v>20.93</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5433,7 +5433,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5526,7 +5526,7 @@
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5557,22 +5557,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920292</v>
+        <v>22330051920386</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="D6" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5580,16 +5580,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920155</v>
+        <v>22330051920386</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5603,19 +5603,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920157</v>
+        <v>22330051920384</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
         <v>66</v>
@@ -5626,39 +5626,39 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920269</v>
+        <v>22330051920157</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>157</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920386</v>
+        <v>22330051920269</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>175</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -5667,7 +5667,7 @@
         <v>64</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -5687,32 +5687,9 @@
         <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920176</v>
-      </c>
-      <c r="B12" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" t="s">
-        <v>144</v>
-      </c>
-      <c r="D12" t="s">
-        <v>185</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1FM - Estadisticos 20221.xlsx
+++ b/grupos/1FM - Estadisticos 20221.xlsx
@@ -3780,7 +3780,7 @@
         <v>8</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K39">
         <v>7</v>

--- a/grupos/1FM - Estadisticos 20221.xlsx
+++ b/grupos/1FM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="186">
   <si>
     <t>Materia</t>
   </si>
@@ -242,289 +242,289 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>CAMARILLO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>CALOCA</t>
+  </si>
+  <si>
+    <t>CALVO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>CORRO</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>LUCIO</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>NATIVIDAD</t>
+  </si>
+  <si>
+    <t>ORTIGOZA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
+    <t>ZAVALA</t>
+  </si>
+  <si>
+    <t>ZAVALETA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>URIAS</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CUAQUEHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>TEQUILIQUIHUA</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>GAMBINO</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
     <t>VILLEGAS</t>
   </si>
   <si>
+    <t>VOTTE</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>ARGUELLES</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>AVALOS</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>DELGADO</t>
+  </si>
+  <si>
+    <t>CAMILA JEZABEL</t>
+  </si>
+  <si>
+    <t>EDUARDO EMER</t>
+  </si>
+  <si>
+    <t>ISAAC ASAEL</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>EDNA YOSSELIN</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>LESLY VIANEY</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>ERICK ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ARLETH MALERY</t>
+  </si>
+  <si>
+    <t>ANGEL EMMANUEL</t>
+  </si>
+  <si>
+    <t>RUFINA ISABEL</t>
+  </si>
+  <si>
+    <t>JESUS EMMANUEL</t>
+  </si>
+  <si>
+    <t>LUIS BRANDON</t>
+  </si>
+  <si>
+    <t>MELANIE</t>
+  </si>
+  <si>
+    <t>GLORIA</t>
+  </si>
+  <si>
+    <t>DINORAH AZUL</t>
+  </si>
+  <si>
+    <t>MARIAM</t>
+  </si>
+  <si>
+    <t>MARIO</t>
+  </si>
+  <si>
+    <t>LLUVIA RUBI</t>
+  </si>
+  <si>
+    <t>MARIA PAULINA</t>
+  </si>
+  <si>
+    <t>WENDY</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>NILO</t>
+  </si>
+  <si>
     <t>IVETTE NAOMI</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BELLO</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>CAMARILLO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CARDENAS</t>
-  </si>
-  <si>
-    <t>CALOCA</t>
-  </si>
-  <si>
-    <t>CALVO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>CORRO</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>LUCIO</t>
-  </si>
-  <si>
-    <t>NATIVIDAD</t>
-  </si>
-  <si>
-    <t>ORTIGOZA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>ZAVALA</t>
-  </si>
-  <si>
-    <t>ZAVALETA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>URIAS</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CUAQUEHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>TEQUILIQUIHUA</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>GAMBINO</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>VOTTE</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>ARGUELLES</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>AVALOS</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
-    <t>CAMILA JEZABEL</t>
-  </si>
-  <si>
-    <t>EDUARDO EMER</t>
-  </si>
-  <si>
-    <t>ISAAC ASAEL</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>EDNA YOSSELIN</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>LESLY VIANEY</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
-  </si>
-  <si>
-    <t>ERICK ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ARLETH MALERY</t>
-  </si>
-  <si>
-    <t>ANGEL EMMANUEL</t>
-  </si>
-  <si>
-    <t>RUFINA ISABEL</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>LUIS BRANDON</t>
-  </si>
-  <si>
-    <t>MELANIE</t>
-  </si>
-  <si>
-    <t>GLORIA</t>
-  </si>
-  <si>
-    <t>DINORAH AZUL</t>
-  </si>
-  <si>
-    <t>MARIAM</t>
-  </si>
-  <si>
-    <t>MARIO</t>
-  </si>
-  <si>
-    <t>LLUVIA RUBI</t>
-  </si>
-  <si>
-    <t>MARIA PAULINA</t>
-  </si>
-  <si>
-    <t>WENDY</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>NILO</t>
   </si>
   <si>
     <t>KAY LEILANI</t>
@@ -3001,7 +3001,7 @@
         <v>7</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H29">
         <v>9</v>
@@ -3019,7 +3019,7 @@
         <v>6</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3055,7 +3055,7 @@
         <v>7</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -4429,13 +4429,13 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2">
         <v>10</v>
       </c>
       <c r="F2">
-        <v>74.42</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="G2">
         <v>23.26</v>
@@ -4444,10 +4444,10 @@
         <v>7</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>2.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4617,7 +4617,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4642,26 +4642,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920269</v>
-      </c>
-      <c r="B2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -4697,30 +4677,30 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920269</v>
+        <v>22330051920149</v>
       </c>
       <c r="B2" t="s">
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920149</v>
+        <v>22330051920150</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D3" t="s">
         <v>145</v>
@@ -4731,13 +4711,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920150</v>
+        <v>22330051920151</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D4" t="s">
         <v>146</v>
@@ -4748,13 +4728,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920151</v>
+        <v>22330051920292</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
         <v>147</v>
@@ -4765,13 +4745,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920292</v>
+        <v>22330051920383</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D6" t="s">
         <v>148</v>
@@ -4782,13 +4762,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920383</v>
+        <v>22330051920153</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
         <v>149</v>
@@ -4799,13 +4779,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920153</v>
+        <v>22330051920155</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
         <v>150</v>
@@ -4816,13 +4796,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920155</v>
+        <v>22330051920156</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
         <v>151</v>
@@ -4833,13 +4813,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920156</v>
+        <v>22330051920154</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
         <v>152</v>
@@ -4850,13 +4830,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920154</v>
+        <v>22330051920381</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D11" t="s">
         <v>153</v>
@@ -4867,13 +4847,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920381</v>
+        <v>22330051920152</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D12" t="s">
         <v>154</v>
@@ -4884,13 +4864,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920152</v>
+        <v>22330051920384</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D13" t="s">
         <v>155</v>
@@ -4901,13 +4881,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920384</v>
+        <v>22330051920157</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
         <v>156</v>
@@ -4918,13 +4898,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920157</v>
+        <v>22330051920161</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D15" t="s">
         <v>157</v>
@@ -4935,13 +4915,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920161</v>
+        <v>22330051920158</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D16" t="s">
         <v>158</v>
@@ -4952,13 +4932,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920158</v>
+        <v>22330051920159</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D17" t="s">
         <v>159</v>
@@ -4969,13 +4949,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920159</v>
+        <v>22330051920162</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
         <v>160</v>
@@ -4986,13 +4966,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920162</v>
+        <v>22330051920160</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="D19" t="s">
         <v>161</v>
@@ -5003,13 +4983,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920160</v>
+        <v>22330051920296</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D20" t="s">
         <v>162</v>
@@ -5020,13 +5000,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920296</v>
+        <v>22330051920163</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="D21" t="s">
         <v>163</v>
@@ -5037,13 +5017,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920163</v>
+        <v>22330051920165</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="D22" t="s">
         <v>164</v>
@@ -5054,13 +5034,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920165</v>
+        <v>22330051920385</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D23" t="s">
         <v>165</v>
@@ -5071,13 +5051,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920385</v>
+        <v>22330051920164</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D24" t="s">
         <v>166</v>
@@ -5088,13 +5068,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920164</v>
+        <v>22330051920267</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D25" t="s">
         <v>167</v>
@@ -5105,16 +5085,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920267</v>
+        <v>22330051920166</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D26" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -5122,16 +5102,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920166</v>
+        <v>22330051920269</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D27" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -5142,10 +5122,10 @@
         <v>22330051920167</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D28" t="s">
         <v>169</v>
@@ -5159,10 +5139,10 @@
         <v>22330051920382</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D29" t="s">
         <v>170</v>
@@ -5176,10 +5156,10 @@
         <v>22330051920168</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="D30" t="s">
         <v>171</v>
@@ -5193,10 +5173,10 @@
         <v>22330051920169</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D31" t="s">
         <v>172</v>
@@ -5210,10 +5190,10 @@
         <v>22330051920170</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D32" t="s">
         <v>173</v>
@@ -5227,10 +5207,10 @@
         <v>22330051920275</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D33" t="s">
         <v>174</v>
@@ -5244,10 +5224,10 @@
         <v>22330051920386</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D34" t="s">
         <v>175</v>
@@ -5261,10 +5241,10 @@
         <v>22330051920172</v>
       </c>
       <c r="B35" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D35" t="s">
         <v>176</v>
@@ -5278,10 +5258,10 @@
         <v>22330051920278</v>
       </c>
       <c r="B36" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D36" t="s">
         <v>177</v>
@@ -5295,10 +5275,10 @@
         <v>22330051920173</v>
       </c>
       <c r="B37" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C37" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D37" t="s">
         <v>178</v>
@@ -5312,10 +5292,10 @@
         <v>22330051920171</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C38" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D38" t="s">
         <v>179</v>
@@ -5329,10 +5309,10 @@
         <v>22330051920174</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C39" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D39" t="s">
         <v>180</v>
@@ -5346,10 +5326,10 @@
         <v>22330051920387</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C40" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D40" t="s">
         <v>181</v>
@@ -5363,10 +5343,10 @@
         <v>22330051920284</v>
       </c>
       <c r="B41" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C41" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D41" t="s">
         <v>182</v>
@@ -5380,10 +5360,10 @@
         <v>22330051920175</v>
       </c>
       <c r="B42" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C42" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D42" t="s">
         <v>183</v>
@@ -5397,10 +5377,10 @@
         <v>22330051920287</v>
       </c>
       <c r="B43" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C43" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D43" t="s">
         <v>184</v>
@@ -5414,10 +5394,10 @@
         <v>22330051920176</v>
       </c>
       <c r="B44" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D44" t="s">
         <v>185</v>
@@ -5433,7 +5413,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5468,13 +5448,13 @@
         <v>22330051920160</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -5491,13 +5471,13 @@
         <v>22330051920160</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5514,10 +5494,10 @@
         <v>22330051920382</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
         <v>170</v>
@@ -5537,10 +5517,10 @@
         <v>22330051920382</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D5" t="s">
         <v>170</v>
@@ -5560,10 +5540,10 @@
         <v>22330051920386</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D6" t="s">
         <v>175</v>
@@ -5583,10 +5563,10 @@
         <v>22330051920386</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D7" t="s">
         <v>175</v>
@@ -5606,13 +5586,13 @@
         <v>22330051920384</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -5629,13 +5609,13 @@
         <v>22330051920157</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -5649,47 +5629,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920269</v>
+        <v>22330051920172</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>176</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920172</v>
-      </c>
-      <c r="B11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" t="s">
-        <v>139</v>
-      </c>
-      <c r="D11" t="s">
-        <v>176</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>66</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1FM - Estadisticos 20221.xlsx
+++ b/grupos/1FM - Estadisticos 20221.xlsx
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1177,7 +1177,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1195,7 +1195,7 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -1254,7 +1254,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1331,7 +1331,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1349,7 +1349,7 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1408,7 +1408,7 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1485,7 +1485,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1562,7 +1562,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1639,7 +1639,7 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1716,7 +1716,7 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1734,7 +1734,7 @@
         <v>8</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>7</v>
@@ -1793,7 +1793,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1870,7 +1870,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1888,7 +1888,7 @@
         <v>8</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1947,7 +1947,7 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -2024,7 +2024,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2042,7 +2042,7 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -2101,7 +2101,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2119,7 +2119,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>7</v>
@@ -2178,7 +2178,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2196,7 +2196,7 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -2255,7 +2255,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2273,7 +2273,7 @@
         <v>6</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>6</v>
@@ -2332,7 +2332,7 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2350,7 +2350,7 @@
         <v>6</v>
       </c>
       <c r="U20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>5</v>
@@ -2409,7 +2409,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2486,7 +2486,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2504,7 +2504,7 @@
         <v>6</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -2563,7 +2563,7 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2640,7 +2640,7 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2717,7 +2717,7 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2794,7 +2794,7 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2871,7 +2871,7 @@
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2889,7 +2889,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V27">
         <v>5</v>
@@ -2948,7 +2948,7 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3025,7 +3025,7 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3102,7 +3102,7 @@
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3179,7 +3179,7 @@
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3197,7 +3197,7 @@
         <v>7</v>
       </c>
       <c r="U31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V31">
         <v>5</v>
@@ -3256,7 +3256,7 @@
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3333,7 +3333,7 @@
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3410,7 +3410,7 @@
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3487,7 +3487,7 @@
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3505,7 +3505,7 @@
         <v>7</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V35">
         <v>6</v>
@@ -3564,7 +3564,7 @@
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3582,7 +3582,7 @@
         <v>7</v>
       </c>
       <c r="U36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V36">
         <v>7</v>
@@ -3641,7 +3641,7 @@
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3718,7 +3718,7 @@
         <v>-1</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -3736,7 +3736,7 @@
         <v>7</v>
       </c>
       <c r="U38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V38">
         <v>9</v>
@@ -3795,7 +3795,7 @@
         <v>-1</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -3872,7 +3872,7 @@
         <v>-1</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P40">
         <v>-1</v>
@@ -3890,7 +3890,7 @@
         <v>7</v>
       </c>
       <c r="U40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V40">
         <v>7</v>
@@ -3949,7 +3949,7 @@
         <v>-1</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P41">
         <v>-1</v>
@@ -4026,7 +4026,7 @@
         <v>-1</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P42">
         <v>-1</v>
@@ -4103,7 +4103,7 @@
         <v>-1</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P43">
         <v>-1</v>
@@ -4121,7 +4121,7 @@
         <v>6</v>
       </c>
       <c r="U43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V43">
         <v>8</v>
@@ -4180,7 +4180,7 @@
         <v>-1</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P44">
         <v>-1</v>
@@ -4257,7 +4257,7 @@
         <v>-1</v>
       </c>
       <c r="O45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P45">
         <v>-1</v>
@@ -4275,7 +4275,7 @@
         <v>6</v>
       </c>
       <c r="U45">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V45">
         <v>7</v>
@@ -4334,7 +4334,7 @@
         <v>-1</v>
       </c>
       <c r="O46">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P46">
         <v>-1</v>
@@ -4352,7 +4352,7 @@
         <v>8</v>
       </c>
       <c r="U46">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V46">
         <v>6</v>
@@ -4601,7 +4601,7 @@
         <v>2.33</v>
       </c>
       <c r="H7">
-        <v>9.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/1FM - Estadisticos 20221.xlsx
+++ b/grupos/1FM - Estadisticos 20221.xlsx
@@ -212,13 +212,13 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
     <t>Herrera Serrano Mayra Iliana</t>
@@ -1097,7 +1097,7 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>10</v>
@@ -1109,10 +1109,10 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -1174,7 +1174,7 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
         <v>5</v>
@@ -1186,13 +1186,13 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -1207,7 +1207,7 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1251,7 +1251,7 @@
         <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
         <v>10</v>
@@ -1263,10 +1263,10 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -1284,7 +1284,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1328,7 +1328,7 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>7</v>
@@ -1340,10 +1340,10 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>6</v>
@@ -1361,7 +1361,7 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1405,7 +1405,7 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>10</v>
@@ -1417,10 +1417,10 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1482,7 +1482,7 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
         <v>7</v>
@@ -1494,10 +1494,10 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>6</v>
@@ -1559,7 +1559,7 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
         <v>10</v>
@@ -1571,10 +1571,10 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1636,7 +1636,7 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>10</v>
@@ -1648,10 +1648,10 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1666,10 +1666,10 @@
         <v>10</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1713,7 +1713,7 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>6</v>
@@ -1725,13 +1725,13 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>8</v>
@@ -1790,7 +1790,7 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
         <v>10</v>
@@ -1802,10 +1802,10 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>7</v>
@@ -1867,7 +1867,7 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -1879,10 +1879,10 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <v>8</v>
@@ -1944,7 +1944,7 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
         <v>10</v>
@@ -1956,10 +1956,10 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>8</v>
@@ -1974,10 +1974,10 @@
         <v>9</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2021,7 +2021,7 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
         <v>6</v>
@@ -2033,10 +2033,10 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>7</v>
@@ -2051,7 +2051,7 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -2098,7 +2098,7 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
         <v>7</v>
@@ -2110,10 +2110,10 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>7</v>
@@ -2128,7 +2128,7 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -2175,7 +2175,7 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>5</v>
@@ -2187,10 +2187,10 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
         <v>6</v>
@@ -2205,7 +2205,7 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2252,7 +2252,7 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O19">
         <v>5</v>
@@ -2264,10 +2264,10 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
         <v>6</v>
@@ -2282,7 +2282,7 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -2329,7 +2329,7 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
         <v>8</v>
@@ -2341,10 +2341,10 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>6</v>
@@ -2362,7 +2362,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2406,7 +2406,7 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>10</v>
@@ -2418,10 +2418,10 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2439,7 +2439,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2483,7 +2483,7 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>5</v>
@@ -2495,10 +2495,10 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
         <v>6</v>
@@ -2513,7 +2513,7 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2560,7 +2560,7 @@
         <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
         <v>10</v>
@@ -2572,13 +2572,13 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>9</v>
@@ -2590,7 +2590,7 @@
         <v>8</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2637,7 +2637,7 @@
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
         <v>10</v>
@@ -2649,10 +2649,10 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
         <v>9</v>
@@ -2670,7 +2670,7 @@
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2714,7 +2714,7 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
         <v>10</v>
@@ -2726,10 +2726,10 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2747,7 +2747,7 @@
         <v>8</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2791,7 +2791,7 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
         <v>10</v>
@@ -2803,10 +2803,10 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
         <v>9</v>
@@ -2824,7 +2824,7 @@
         <v>7</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2868,7 +2868,7 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
         <v>5</v>
@@ -2880,13 +2880,13 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U27">
         <v>6</v>
@@ -2898,7 +2898,7 @@
         <v>5</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y27">
         <v>5</v>
@@ -2945,7 +2945,7 @@
         <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
         <v>5</v>
@@ -2957,10 +2957,10 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
         <v>5</v>
@@ -3022,7 +3022,7 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
         <v>10</v>
@@ -3034,10 +3034,10 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
         <v>8</v>
@@ -3052,10 +3052,10 @@
         <v>8</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3099,7 +3099,7 @@
         <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
         <v>10</v>
@@ -3111,13 +3111,13 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U30">
         <v>10</v>
@@ -3129,10 +3129,10 @@
         <v>8</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3176,7 +3176,7 @@
         <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>6</v>
@@ -3188,10 +3188,10 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>7</v>
@@ -3209,7 +3209,7 @@
         <v>6</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3253,7 +3253,7 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
         <v>10</v>
@@ -3265,10 +3265,10 @@
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -3330,7 +3330,7 @@
         <v>6</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>10</v>
@@ -3342,10 +3342,10 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3360,7 +3360,7 @@
         <v>9</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y33">
         <v>8</v>
@@ -3407,7 +3407,7 @@
         <v>8</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
         <v>10</v>
@@ -3419,10 +3419,10 @@
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
         <v>9</v>
@@ -3484,7 +3484,7 @@
         <v>5</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O35">
         <v>5</v>
@@ -3496,13 +3496,13 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U35">
         <v>7</v>
@@ -3517,7 +3517,7 @@
         <v>6</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3561,7 +3561,7 @@
         <v>5</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O36">
         <v>6</v>
@@ -3573,10 +3573,10 @@
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T36">
         <v>7</v>
@@ -3594,7 +3594,7 @@
         <v>6</v>
       </c>
       <c r="Y36">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3638,7 +3638,7 @@
         <v>7</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O37">
         <v>10</v>
@@ -3650,10 +3650,10 @@
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T37">
         <v>8</v>
@@ -3715,7 +3715,7 @@
         <v>6</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O38">
         <v>8</v>
@@ -3727,10 +3727,10 @@
         <v>-1</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T38">
         <v>7</v>
@@ -3792,7 +3792,7 @@
         <v>6</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O39">
         <v>7</v>
@@ -3804,13 +3804,13 @@
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U39">
         <v>8</v>
@@ -3825,7 +3825,7 @@
         <v>7</v>
       </c>
       <c r="Y39">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3869,7 +3869,7 @@
         <v>6</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O40">
         <v>9</v>
@@ -3881,13 +3881,13 @@
         <v>-1</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U40">
         <v>9</v>
@@ -3946,7 +3946,7 @@
         <v>9</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O41">
         <v>10</v>
@@ -3958,10 +3958,10 @@
         <v>-1</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T41">
         <v>10</v>
@@ -4023,7 +4023,7 @@
         <v>6</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O42">
         <v>10</v>
@@ -4035,13 +4035,13 @@
         <v>-1</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U42">
         <v>9</v>
@@ -4056,7 +4056,7 @@
         <v>8</v>
       </c>
       <c r="Y42">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -4100,7 +4100,7 @@
         <v>8</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O43">
         <v>7</v>
@@ -4112,10 +4112,10 @@
         <v>-1</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T43">
         <v>6</v>
@@ -4133,7 +4133,7 @@
         <v>6</v>
       </c>
       <c r="Y43">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -4177,7 +4177,7 @@
         <v>8</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O44">
         <v>10</v>
@@ -4189,10 +4189,10 @@
         <v>-1</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T44">
         <v>8</v>
@@ -4207,10 +4207,10 @@
         <v>9</v>
       </c>
       <c r="X44">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y44">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -4254,7 +4254,7 @@
         <v>6</v>
       </c>
       <c r="N45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O45">
         <v>10</v>
@@ -4266,10 +4266,10 @@
         <v>-1</v>
       </c>
       <c r="R45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T45">
         <v>6</v>
@@ -4284,7 +4284,7 @@
         <v>8</v>
       </c>
       <c r="X45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y45">
         <v>6</v>
@@ -4331,7 +4331,7 @@
         <v>5</v>
       </c>
       <c r="N46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O46">
         <v>10</v>
@@ -4343,13 +4343,13 @@
         <v>-1</v>
       </c>
       <c r="R46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T46">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U46">
         <v>9</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
@@ -4429,19 +4429,19 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>76.73999999999999</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="G2">
-        <v>23.26</v>
+        <v>20.93</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4452,7 +4452,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -4473,7 +4473,7 @@
         <v>20.93</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -4493,19 +4493,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>79.06999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G4">
-        <v>20.93</v>
+        <v>18.6</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4525,16 +4525,16 @@
         <v>43</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>86.05</v>
+        <v>90.7</v>
       </c>
       <c r="G5">
-        <v>13.95</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H5">
         <v>6.8</v>
@@ -5445,22 +5445,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920160</v>
+        <v>22330051920161</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5468,19 +5468,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920160</v>
+        <v>22330051920161</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>64</v>
@@ -5491,22 +5491,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920382</v>
+        <v>22330051920172</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C4" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D4" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5514,22 +5514,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920382</v>
+        <v>22330051920172</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5537,19 +5537,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920386</v>
+        <v>22330051920384</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D6" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>65</v>
@@ -5560,19 +5560,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920386</v>
+        <v>22330051920157</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="D7" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
         <v>64</v>
@@ -5583,19 +5583,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920384</v>
+        <v>22330051920160</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D8" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>66</v>
@@ -5606,19 +5606,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920157</v>
+        <v>22330051920382</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
         <v>65</v>
@@ -5629,22 +5629,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920172</v>
+        <v>22330051920386</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G10">
         <v>5</v>

--- a/grupos/1FM - Estadisticos 20221.xlsx
+++ b/grupos/1FM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="186">
   <si>
     <t>Materia</t>
   </si>
@@ -212,10 +212,10 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
     <t>González Altamirano Victorino Juventino</t>
@@ -1103,7 +1103,7 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -1180,7 +1180,7 @@
         <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -1257,7 +1257,7 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -1334,7 +1334,7 @@
         <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1411,7 +1411,7 @@
         <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1429,7 +1429,7 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1488,7 +1488,7 @@
         <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1565,7 +1565,7 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1642,7 +1642,7 @@
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1719,7 +1719,7 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1737,7 +1737,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1796,7 +1796,7 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1873,7 +1873,7 @@
         <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1950,7 +1950,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -2027,7 +2027,7 @@
         <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -2104,7 +2104,7 @@
         <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -2181,7 +2181,7 @@
         <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -2258,7 +2258,7 @@
         <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -2276,7 +2276,7 @@
         <v>6</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>7</v>
@@ -2335,7 +2335,7 @@
         <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2412,7 +2412,7 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2489,7 +2489,7 @@
         <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2507,7 +2507,7 @@
         <v>6</v>
       </c>
       <c r="V22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>5</v>
@@ -2566,7 +2566,7 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -2584,7 +2584,7 @@
         <v>9</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -2643,7 +2643,7 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -2720,7 +2720,7 @@
         <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -2797,7 +2797,7 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -2815,7 +2815,7 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2874,7 +2874,7 @@
         <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -2951,7 +2951,7 @@
         <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -3028,7 +3028,7 @@
         <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -3046,7 +3046,7 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -3105,7 +3105,7 @@
         <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -3182,7 +3182,7 @@
         <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -3259,7 +3259,7 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -3336,7 +3336,7 @@
         <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3413,7 +3413,7 @@
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -3490,7 +3490,7 @@
         <v>5</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -3567,7 +3567,7 @@
         <v>6</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -3585,7 +3585,7 @@
         <v>8</v>
       </c>
       <c r="V36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W36">
         <v>7</v>
@@ -3644,7 +3644,7 @@
         <v>10</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
         <v>-1</v>
@@ -3662,7 +3662,7 @@
         <v>10</v>
       </c>
       <c r="V37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W37">
         <v>9</v>
@@ -3721,7 +3721,7 @@
         <v>8</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q38">
         <v>-1</v>
@@ -3798,7 +3798,7 @@
         <v>7</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q39">
         <v>-1</v>
@@ -3875,7 +3875,7 @@
         <v>9</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q40">
         <v>-1</v>
@@ -3952,7 +3952,7 @@
         <v>10</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q41">
         <v>-1</v>
@@ -4029,7 +4029,7 @@
         <v>10</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q42">
         <v>-1</v>
@@ -4106,7 +4106,7 @@
         <v>7</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q43">
         <v>-1</v>
@@ -4124,7 +4124,7 @@
         <v>9</v>
       </c>
       <c r="V43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W43">
         <v>8</v>
@@ -4183,7 +4183,7 @@
         <v>10</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q44">
         <v>-1</v>
@@ -4201,7 +4201,7 @@
         <v>10</v>
       </c>
       <c r="V44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W44">
         <v>9</v>
@@ -4260,7 +4260,7 @@
         <v>10</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q45">
         <v>-1</v>
@@ -4278,7 +4278,7 @@
         <v>8</v>
       </c>
       <c r="V45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W45">
         <v>8</v>
@@ -4337,7 +4337,7 @@
         <v>10</v>
       </c>
       <c r="P46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q46">
         <v>-1</v>
@@ -4355,7 +4355,7 @@
         <v>9</v>
       </c>
       <c r="V46">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W46">
         <v>5</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
@@ -4429,19 +4429,19 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>79.06999999999999</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="G2">
-        <v>20.93</v>
+        <v>23.26</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4452,7 +4452,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -4473,7 +4473,7 @@
         <v>20.93</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5413,7 +5413,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5460,7 +5460,7 @@
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5483,7 +5483,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5491,22 +5491,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920172</v>
+        <v>22330051920160</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5514,16 +5514,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920172</v>
+        <v>22330051920160</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="D5" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5537,19 +5537,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920384</v>
+        <v>22330051920296</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
         <v>65</v>
@@ -5560,22 +5560,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920157</v>
+        <v>22330051920296</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5583,22 +5583,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920160</v>
+        <v>22330051920172</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="D8" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5606,22 +5606,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920382</v>
+        <v>22330051920172</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D9" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5629,24 +5629,93 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920386</v>
+        <v>22330051920384</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D10" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
         <v>64</v>
       </c>
       <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920157</v>
+      </c>
+      <c r="B11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11" t="s">
+        <v>156</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920382</v>
+      </c>
+      <c r="B12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D12" t="s">
+        <v>170</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920386</v>
+      </c>
+      <c r="B13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" t="s">
+        <v>137</v>
+      </c>
+      <c r="D13" t="s">
+        <v>175</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1FM - Estadisticos 20221.xlsx
+++ b/grupos/1FM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="186">
   <si>
     <t>Materia</t>
   </si>
@@ -215,10 +215,10 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
     <t>Herrera Serrano Mayra Iliana</t>
@@ -1106,7 +1106,7 @@
         <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>10</v>
@@ -1183,7 +1183,7 @@
         <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <v>9</v>
@@ -1260,7 +1260,7 @@
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>8</v>
@@ -1337,7 +1337,7 @@
         <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
         <v>8</v>
@@ -1414,7 +1414,7 @@
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>8</v>
@@ -1491,7 +1491,7 @@
         <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
         <v>5</v>
@@ -1568,7 +1568,7 @@
         <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>7</v>
@@ -1645,7 +1645,7 @@
         <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>8</v>
@@ -1722,7 +1722,7 @@
         <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
         <v>6</v>
@@ -1799,7 +1799,7 @@
         <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
         <v>6</v>
@@ -1876,7 +1876,7 @@
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>6</v>
@@ -1894,7 +1894,7 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1953,7 +1953,7 @@
         <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>7</v>
@@ -1971,7 +1971,7 @@
         <v>8</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -2030,7 +2030,7 @@
         <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>8</v>
@@ -2048,7 +2048,7 @@
         <v>7</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -2107,7 +2107,7 @@
         <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <v>8</v>
@@ -2125,7 +2125,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -2184,7 +2184,7 @@
         <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <v>7</v>
@@ -2261,7 +2261,7 @@
         <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
         <v>8</v>
@@ -2338,7 +2338,7 @@
         <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>7</v>
@@ -2356,7 +2356,7 @@
         <v>5</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -2415,7 +2415,7 @@
         <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
         <v>7</v>
@@ -2492,7 +2492,7 @@
         <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>8</v>
@@ -2569,7 +2569,7 @@
         <v>6</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>6</v>
@@ -2646,7 +2646,7 @@
         <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
         <v>6</v>
@@ -2723,7 +2723,7 @@
         <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
         <v>8</v>
@@ -2800,7 +2800,7 @@
         <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
         <v>7</v>
@@ -2877,7 +2877,7 @@
         <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
         <v>5</v>
@@ -2954,7 +2954,7 @@
         <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
         <v>5</v>
@@ -3031,7 +3031,7 @@
         <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
         <v>5</v>
@@ -3108,7 +3108,7 @@
         <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
         <v>7</v>
@@ -3185,7 +3185,7 @@
         <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
         <v>6</v>
@@ -3262,7 +3262,7 @@
         <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
         <v>8</v>
@@ -3339,7 +3339,7 @@
         <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
         <v>9</v>
@@ -3416,7 +3416,7 @@
         <v>9</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
         <v>9</v>
@@ -3434,7 +3434,7 @@
         <v>9</v>
       </c>
       <c r="W34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>8</v>
@@ -3493,7 +3493,7 @@
         <v>7</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
         <v>6</v>
@@ -3511,7 +3511,7 @@
         <v>6</v>
       </c>
       <c r="W35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X35">
         <v>6</v>
@@ -3570,7 +3570,7 @@
         <v>5</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
         <v>6</v>
@@ -3647,7 +3647,7 @@
         <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
         <v>8</v>
@@ -3665,7 +3665,7 @@
         <v>8</v>
       </c>
       <c r="W37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X37">
         <v>7</v>
@@ -3724,7 +3724,7 @@
         <v>8</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R38">
         <v>7</v>
@@ -3801,7 +3801,7 @@
         <v>5</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R39">
         <v>6</v>
@@ -3878,7 +3878,7 @@
         <v>9</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R40">
         <v>6</v>
@@ -3896,7 +3896,7 @@
         <v>7</v>
       </c>
       <c r="W40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X40">
         <v>7</v>
@@ -3955,7 +3955,7 @@
         <v>10</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R41">
         <v>10</v>
@@ -3973,7 +3973,7 @@
         <v>10</v>
       </c>
       <c r="W41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X41">
         <v>9</v>
@@ -4032,7 +4032,7 @@
         <v>8</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R42">
         <v>7</v>
@@ -4109,7 +4109,7 @@
         <v>5</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R43">
         <v>6</v>
@@ -4127,7 +4127,7 @@
         <v>7</v>
       </c>
       <c r="W43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X43">
         <v>6</v>
@@ -4186,7 +4186,7 @@
         <v>7</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R44">
         <v>7</v>
@@ -4204,7 +4204,7 @@
         <v>8</v>
       </c>
       <c r="W44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X44">
         <v>7</v>
@@ -4263,7 +4263,7 @@
         <v>5</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R45">
         <v>6</v>
@@ -4340,7 +4340,7 @@
         <v>5</v>
       </c>
       <c r="Q46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R46">
         <v>5</v>
@@ -4452,7 +4452,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -4461,19 +4461,19 @@
         <v>43</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>79.06999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G3">
-        <v>20.93</v>
+        <v>18.6</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -4493,19 +4493,19 @@
         <v>43</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>81.40000000000001</v>
+        <v>86.05</v>
       </c>
       <c r="G4">
-        <v>18.6</v>
+        <v>13.95</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5413,7 +5413,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5445,16 +5445,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920161</v>
+        <v>22330051920160</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5468,19 +5468,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920161</v>
+        <v>22330051920160</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>65</v>
@@ -5491,22 +5491,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920160</v>
+        <v>22330051920296</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5514,22 +5514,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920160</v>
+        <v>22330051920296</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5537,22 +5537,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920296</v>
+        <v>22330051920172</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="D6" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5560,22 +5560,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920296</v>
+        <v>22330051920172</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="D7" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5583,16 +5583,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920172</v>
+        <v>22330051920384</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="D8" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -5606,22 +5606,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920172</v>
+        <v>22330051920161</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="D9" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5629,16 +5629,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920384</v>
+        <v>22330051920382</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -5647,75 +5647,6 @@
         <v>64</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920157</v>
-      </c>
-      <c r="B11" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D11" t="s">
-        <v>156</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920382</v>
-      </c>
-      <c r="B12" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" t="s">
-        <v>134</v>
-      </c>
-      <c r="D12" t="s">
-        <v>170</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920386</v>
-      </c>
-      <c r="B13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" t="s">
-        <v>137</v>
-      </c>
-      <c r="D13" t="s">
-        <v>175</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>65</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1FM - Estadisticos 20221.xlsx
+++ b/grupos/1FM - Estadisticos 20221.xlsx
@@ -68,7 +68,7 @@
     <t>BELLO MORALES JOSUE</t>
   </si>
   <si>
-    <t>CALOCA TEXCAHUA ARLETH MALERY</t>
+    <t>CALOCA TEXCAHUA ARLETH MARELY</t>
   </si>
   <si>
     <t>CALVO URIAS ANGEL EMMANUEL</t>
@@ -479,7 +479,7 @@
     <t>ERICK ALEJANDRO</t>
   </si>
   <si>
-    <t>ARLETH MALERY</t>
+    <t>ARLETH MARELY</t>
   </si>
   <si>
     <t>ANGEL EMMANUEL</t>
